--- a/pharma_resultats.xlsx
+++ b/pharma_resultats.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -528,22 +528,22 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pharmacie Chy</t>
+          <t>Pharmacie Broche Rosellini</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>760 Av Maurice Dauvergne</t>
+          <t>Boulevard Pierre Pasquini</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>77350</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Le Mee Sur Seine</t>
+          <t>L ILE ROUSSE</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -558,42 +558,48 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>760 Av. Maurice Dauvergne, 77350 Le Mée-sur-Seine, France</t>
+          <t>Boulevard Pierre Pasquini Résidence Isola Celeste, 20220 L'Île-Rousse, France</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>+33 1 60 68 11 06</t>
+          <t>+33 4 95 60 00 06</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>08:30–19:20</t>
+          <t>08:30–12:30
+14:30–19:30</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>08:30–19:20</t>
+          <t>08:30–12:30
+14:30–19:30</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>08:30–19:20</t>
+          <t>08:30–12:30
+14:30–19:30</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Fermé</t>
+          <t>08:30–12:30
+14:30–19:30</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Fermé</t>
+          <t>08:30–12:30
+14:30–19:30</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Fermé</t>
+          <t>09:00–12:30
+15:00–19:30</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -602,28 +608,28 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.7096153846153845</v>
+        <v>0.8227272727272726</v>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Pharmacie Talarczyk</t>
+          <t>Pharmacie Chainieux</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>70 Rue Casimir Beugnet</t>
+          <t>1601 route de Nimes</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>62160</t>
+          <t>30560</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>GRENAY</t>
+          <t>Saint-Hilaire-de-Brethmas</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -638,41 +644,41 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>70 Rue Casimir Beugnet, 62160 Grenay, France</t>
+          <t>1601 Rte de Nîmes, 30560 Saint-Hilaire-de-Brethmas, France</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>+33 3 21 29 10 96</t>
+          <t>+33 4 66 61 05 81</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:00
+          <t>08:30–12:30
 14:00–19:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:00
+          <t>08:30–12:30
 14:00–19:00</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:00
+          <t>08:30–12:30
 14:00–19:00</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:00
+          <t>08:30–12:30
 14:00–19:00</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:00
+          <t>08:30–12:30
 14:00–19:00</t>
         </is>
       </c>
@@ -687,28 +693,28 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.90625</v>
+        <v>0.7582222222222221</v>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Grande Pharmacie Du Pont De L'eure</t>
+          <t>Pharmacie Des Remparts</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>18 Rue Edouard Isambard</t>
+          <t>22 Rue Lallouette</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Pacy Sur Eure</t>
+          <t>Marle</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -723,47 +729,47 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18 Rue Edouard Isambard, 27120 Pacy-sur-Eure, France</t>
+          <t>22 Rue Lalouette, 02250 Marle, France</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>+33 2 32 36 01 08</t>
+          <t>+33 3 23 20 01 16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14:30–19:00</t>
+          <t>08:45–12:15
+14:00–19:00</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:30
-14:30–19:00</t>
+          <t>08:45–12:15
+14:00–19:00</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:30
-14:30–19:00</t>
+          <t>08:45–12:15
+14:00–19:00</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:30
-14:30–19:00</t>
+          <t>08:45–12:15
+14:00–19:00</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:30
-14:30–19:00</t>
+          <t>08:45–12:15
+14:00–19:00</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:30
-14:30–19:00</t>
+          <t>08:45–12:15</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -772,28 +778,28 @@
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.8890410958904109</v>
+        <v>0.8846153846153846</v>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Pharmacie De Firmis</t>
+          <t>Pharmacie lourmel</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>41 Chem. de la Terrasse</t>
+          <t>105 Avenue Felix Faure</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31500</t>
+          <t>75015</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>TOULOUSE</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -808,602 +814,7814 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41 Chem. de la Terrasse, 31500 Toulouse, France</t>
+          <t>105 Av. Félix Faure, 75015 Paris, France</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>+33 5 61 80 07 74</t>
+          <t>+33 1 45 57 45 45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:30
-14:30–19:30</t>
+          <t>09:00–20:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:30
-14:30–19:30</t>
+          <t>09:00–20:00</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:30
-14:30–19:30</t>
+          <t>09:00–20:00</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:30
-14:30–19:30</t>
+          <t>09:00–20:00</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:30
-14:30–19:30</t>
+          <t>09:00–20:00</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>09:00–12:30
-14:30–19:30</t>
+          <t>09:00–20:00</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Fermé</t>
+          <t>08:00–21:00</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.7976849937990904</v>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>Pharmacie Des Blagis</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>51 Rue De Bagneux</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>92330</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>SCEAUX</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>51 Rue de Bagneux, 92330 Sceaux, France</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 46 61 10 59</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–20:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–20:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–20:00</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–20:00</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–20:00</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Raynal</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Place du Village</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>48600</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Bel-Air-Val-d'Ance</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Village, 48600 Bel-Air-Val-d'Ance, France</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 66 69 61 11</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+15:00–19:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+15:00–19:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+15:00–19:00</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+15:00–18:00</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0.7763636363636364</v>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Porte De Chinon</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>71 Rue Porte De Chinon</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>86200</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Loudun</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71 Rue de la Prte de Chinon, 86200 Loudun, France</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>+33 5 49 98 10 67</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:00</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0.7076086956521739</v>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Khun Bay 1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Centre de Loisirs Bay 1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>77200</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Torcy</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Centre de Loisirs Bay, 1 Prom. du 7e Art, 77200 Torcy, France</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 60 05 86 36</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:45</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:45</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:45</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:45</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>09:00–00:00</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>00:00–20:45</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:45</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>0.8072826086956522</v>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Vauban 59370</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Place Vauban</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>59370</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>MONS EN BAROEUL</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Place Vauban, 59370 Mons-en-Barœul, France</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.6595141700404857</v>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Tauleigne</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>10 Place Du General De Gaulle</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7120</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>RUOMS</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>10 Pl. du Général de Gaulle, 07120 Ruoms, France</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 75 39 62 39</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0.9108108108108108</v>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Des 5K</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>22 Bis Rue D' Alsace</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>92300</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Levallois Perret</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>22 bis Rue d'Alsace, 92300 Levallois-Perret, France</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 47 39 41 46</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:30</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:30</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:30</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:00</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:30</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0.622549019607843</v>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Chy</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>760 Av Maurice Dauvergne</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>77350</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Le Mee Sur Seine</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>760 Av. Maurice Dauvergne, 77350 Le Mée-sur-Seine, France</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 60 68 11 06</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:20</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:20</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:20</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0.7096153846153845</v>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Talarczyk</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>70 Rue Casimir Beugnet</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>62160</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>GRENAY</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>70 Rue Casimir Beugnet, 62160 Grenay, France</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 21 29 10 96</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0.90625</v>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Grande Pharmacie Du Pont De L'eure</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>18 Rue Edouard Isambard</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>27120</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Pacy Sur Eure</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>18 Rue Edouard Isambard, 27120 Pacy-sur-Eure, France</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 32 36 01 08</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>14:30–19:00</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0.8890410958904109</v>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De Firmis</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>41 Chem. de la Terrasse</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>31500</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>TOULOUSE</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41 Chem. de la Terrasse, 31500 Toulouse, France</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>+33 5 61 80 07 74</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>Pharmacie Du Village</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>8 Place Du Village</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>38180</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>SEYSSINS</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>trouvé</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>8 Pl. du Village, 38180 Seyssins, France</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>+33 4 76 21 55 55</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>08:15–12:30
 14:30–19:00</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>08:15–12:30
 14:30–19:00</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>08:15–12:30
 14:30–19:00</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>08:15–12:30
 14:30–19:00</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>08:15–12:30
 14:30–19:00</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>08:30–12:30</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Fermé</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="n">
         <v>0.8636363636363635</v>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Pharmacie Des Favignolles</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>1 Rue Leonard De Vinci</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>41200</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Romorantin Lanthenay</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>trouvé</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>86 Av. de Villefranche, 41200 Romorantin-Lanthenay, France</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>+33 2 54 76 00 45</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>09:00–12:30
 14:00–20:00</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>08:30–12:30
 14:00–20:00</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>08:30–12:30
 14:00–20:00</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>08:30–12:30
 14:00–20:00</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>08:30–13:00
 14:00–20:00</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Fermé</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Fermé</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="n">
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="n">
         <v>0.7857142857142857</v>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Pharmacie Du Pays D Olmes</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>2 Chemin De Laouzet</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>9300</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Villeneuve D Olmes</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>trouvé</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>2 Chem. du Laouzet, 09300 Villeneuve-d'Olmes, France</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>+33 5 61 01 05 95</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>08:30–12:30
 14:00–19:30</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>08:30–12:30
 14:00–19:30</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>08:30–12:30
 14:00–19:30</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>08:30–12:30
 14:00–19:30</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>08:30–12:30
 14:00–19:30</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>08:30–12:30
 14:00–18:00</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Fermé</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="n">
         <v>0.7876050420168067</v>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Pharmacie Du Rond Point</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>68 Rue De Brement</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>93130</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Noisy Le Sec</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>trouvé</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>68 Rue de Brément, 93130 Noisy-le-Sec, France</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>+33 1 48 46 65 00</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>09:00–13:00
 14:00–19:30</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>09:00–13:00
 14:00–19:30</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>09:00–13:00
 14:00–19:30</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>09:00–13:00
 14:00–19:30</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>09:00–13:00
 14:00–19:30</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Fermé</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Fermé</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n">
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="n">
         <v>0.8699999999999999</v>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Pharmacie Des Sept Cantons</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>1 Rue Montpensier</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>64000</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>PAU</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>trouvé</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1 Rue Montpensier, 64000 Pau, France</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>+33 5 59 27 71 91</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>08:30–19:30</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>08:30–19:30</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>08:30–19:30</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>08:30–19:30</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>08:30–19:30</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>08:30–19:30</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Fermé</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>0.8150943396226414</v>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Grande Pharmacie De L'europe</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Rue de l'Europe</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>67230</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>BENFELD</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>trouvé</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Rue de l'Europe, 67230 Benfeld, France</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>+33 3 88 74 41 63</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>08:00–20:00</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>08:00–20:00</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>08:00–20:00</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>08:00–20:00</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>08:00–20:00</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>08:00–20:00</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Fermé</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>0.7138199858256555</v>
       </c>
     </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Pharmacie Lachere</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Boulevard De L Europe</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>59820</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>GRAVELINES</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>centre commercial du Polder Sportica, 59820 Gravelines, France</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 28 65 30 74</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:15–19:00</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:15–19:00</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:15–19:00</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:15–19:00</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:15–19:00</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.7666666666666666</v>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De L'indien</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>12 Avenue Du Président John Kennedy</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>45100</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Orléans</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>12 Av. du Président John Kennedy, 45100 Orléans, France</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 38 64 22 32</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:15</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:15</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:15</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:15</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:15</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.9137931034482758</v>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Coudekerque</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>RUE JACQUARD</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>59210</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>COUDEKERQUE-BRANCHE</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Centre Commercial Cora, Rue Jacquard, 59210 Coudekerque-Branche, France</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 28 64 26 68</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:00</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:00</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:00</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:00</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:00</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:00</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0.7566666666666666</v>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Principale</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>4 Rue Du Neufeld</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>67230</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>57450</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>FAREBERSVILLER</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>non trouvé</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="3" t="n">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="3" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Du Stade</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>11 Rue Jesse Owens</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>93200</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>La Plaine St Denis</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>11 Rue Jesse Owens, 93200 Saint-Denis, France</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 48 20 15 62</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>09:30–19:00</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>09:30–19:00</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>09:30–19:00</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>09:30–19:00</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>09:30–19:00</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0.6683535281539558</v>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Bleue</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Cc Auchan - Rue Berthelot</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>78310</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>MAUREPAS</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1 Avenue Johannes Gutenberg Maurepas Pariwest, 78310 Maurepas, France</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 30 66 33 88</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>09:00–21:00</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>09:00–21:00</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>09:00–21:00</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>09:00–21:00</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>09:00–21:00</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>09:00–21:00</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>0.6504761904761904</v>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Orleans</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>73 Rue D Orleans</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>49400</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Saumur</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>non trouvé</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De L Avenue</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>303 Avenue De Firminy</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>43110</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>AUREC SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>303 Av. de Firminy, 43110 Aurec-sur-Loire, France</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 77 35 40 35</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:15
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:15
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:15
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:15
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:15
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:15</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>0.8522388059701492</v>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Ck</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>31 Avenue Le Foll</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>94290</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>VILLENEUVE LE ROI</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>non trouvé</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Bruno-jacquot</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>40 Boulevard Georges Clemenceau</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>54000</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>NANCY</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>40 Bd Georges Clemenceau, 54000 Nancy, France</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 83 51 04 27</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>14:30–19:00</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>09:30–12:00
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>09:30–12:00
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>09:30–12:00
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>09:30–12:00
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>09:30–12:00</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>0.6318827301878149</v>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De L'eglise</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>6 Place De L Eglise</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>60550</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Verneuil En Halatte</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>6 Pl. de l'Église, 60550 Verneuil-en-Halatte, France</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 44 24 32 32</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–16:30</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>0.8411764705882352</v>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Du Carré Diderot</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>23 rue de neuilly</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>92000</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>NANTERRE</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>23 Rue de Neuilly, 92000 Nanterre, France</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 47 29 13 85</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>0.8821428571428571</v>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Clemenceau</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>4 Bd Georges Clemenceau</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>27400</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Louviers</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>4 Bd Georges Clemenceau, 27400 Louviers, France</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 32 40 00 06</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+14:30–18:30</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+14:30–18:30</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+14:30–18:30</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+14:30–18:30</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>0.9029411764705881</v>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Du Marché</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>5 Cours De La Republique</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>13120</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Gardanne</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>5 Cr de la République, 13120 Gardanne, France</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 42 58 30 14</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:15</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:15</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:15</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:15</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:15</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>0.8880597014925373</v>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Pont Rouge</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>21 Place Jean Monnet</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>38640</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>CLAIX</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>21 Pl. Jean Monnet, 38640 Claix, France</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 76 98 03 98</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>0.8821428571428571</v>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De Chaniers</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>21 Avenue Charles De Gaulle</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>17610</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>CHANIERS</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>non trouvé</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Lasfargeas</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>8 Place De La Poste</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>23800</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>DUN LE PALESTEL</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>8 Pl. de la Poste, 23800 Dun-le-Palestel, France</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>+33 5 55 89 14 22</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Leneutre</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>7 Le Beugnon</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>25570</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>GRAND COMBE CHATELEU</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>7 Le Beugnon, 25570 Grand'Combe-Châteleu, France</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 81 68 84 81</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>0.6010610079575597</v>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De Maillane</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>80 Route de Chateaurenard</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>13910</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>MAILLANE</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>D5, Route De Châteaurenard 80, 13910 Maillane, France</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 90 95 74 26</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:15–19:15</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:15–19:15</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:15–19:15</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:15–19:15</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:15–19:15</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.8125714285714285</v>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Des Jumeaux</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1107 Rue Saint Michel</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>88470</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>ST MICHEL SUR MEURTHE</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1107 Rue Saint-Michel, 88470 Saint-Michel-sur-Meurthe, France</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 29 58 30 46</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>0.7575</v>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De La Puisaye</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>24 Place des Frères, Rue Emile Genet</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>89130</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Toucy</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>24 Rue Emile Genet, 89130 Toucy, France</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 86 44 14 11</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:00</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:00</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:00</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:00</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:00</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>08:30–18:00</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>0.7607142857142857</v>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>pharmacie de pont sur seine ( SELARL pharmacie BELLENGER )</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>14 Grande Rue</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>10400</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Pont Sur Seine</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>14 Gr Grande Rue, 10400 Pont-sur-Seine, France</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 25 21 41 14</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+16:00–19:30</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>0.6701754385964912</v>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De La Bruche</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>76 Rue Du General De Gaulle</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>67120</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>DUTTLENHEIM</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>76 Rue Gén de Gaulle, 67120 Duttlenheim, France</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 88 50 81 42</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>08:30–13:00</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>0.8666666666666666</v>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Du Rove</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>64 Route Nationale 568</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>13740</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>LE ROVE</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>64 D568, 13740 Le Rove, France</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 91 46 90 35</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.7839999999999999</v>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De La Monneraye</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Cc Avenue De La Monneraye</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>44410</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Herbignac</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>7 Av. de la Monneraye (RD33), 44410 Herbignac, France</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 40 88 86 10</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:30</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:30</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:30</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:30</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:30</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>0.8561643835616438</v>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Centrale</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Pôle santé, 23 Av. Maréchal Leclerc</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>7700</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>BOURG ST ANDEOL</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Pôle santé, 23 Av. Maréchal Leclerc, 07700 Bourg-Saint-Andéol, France</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 75 54 50 25</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>0.8020408163265306</v>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De Lombron</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>39 rue De Torcé</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>72450</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Lombron</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>39 Rue de Torcé, 72450 Lombron, France</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 43 76 62 75</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>0.8764705882352941</v>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Charpentier</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>82 rue de la Cossonnière</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>45650</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Saint Jean Le Blanc</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>82 Rue de la Cossonnière, 45650 Saint-Jean-le-Blanc, France</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 38 51 12 21</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>14:00–19:30</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–18:00</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>0.8777777777777778</v>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Du Petit-noir</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>2 Rue Du Canal</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>39120</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Petit Noir</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>5 TER Rue de la Mairie, 39120 Petit-Noir, France</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 84 81 61 84</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:15–19:00</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:15–19:00</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:15–19:00</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:15–19:00</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:15–19:00</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>0.7682608695652173</v>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Goudon</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>14 Rue Marcellin Parigot</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>89210</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Brienon Sur Armancon</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>14 Rue Marcellin Parigot, 89210 Brienon-sur-Armançon, France</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 86 56 12 03</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+14:00–18:00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="n">
+        <v>0.8756097560975609</v>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Dupuis</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Cc Carrefour - Avenue Georges Guynemer</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>62100</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>CALAIS</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>non trouvé</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Porte Neuve</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>20 Rue Porte Neuve</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>62200</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>BOULOGNE SUR MER</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>20 Rue de la Prte Neuve, 62200 Boulogne-sur-Mer, France</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 21 31 50 45</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="n">
+        <v>0.8436619718309859</v>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Des Coquelicots</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>43 Avenue Charles Rouxel</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>77340</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Pontault Combault</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>43 Av. Charles Rouxel, 77340 Pontault-Combault, France</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>14:30–20:30</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:30–20:30</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:30–20:30</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:30–20:30</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:30–20:30</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:30–20:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Granet Hunault</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Cc La Massonniere</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>72230</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Monce En Belin</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>La Massonnière, 72230 Moncé-en-Belin, France</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 43 42 84 22</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="n">
+        <v>0.8423728813559321</v>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Djeumo</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>2 Rue Pierre De Coubertin</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>91330</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Yerres</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>2 Rue Pierre de Coubertin, 91330 Yerres, France</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 69 48 82 70</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>09:00–19:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="n">
+        <v>0.8245421245421245</v>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Des Promenades</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2 Faubourg De Marcy</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>58210</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>VARZY</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2 Rue du Fbg de Marcy, 58210 Varzy, France</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 86 29 42 02</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="n">
+        <v>0.8423728813559321</v>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De La Madeleine</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Avenue Marcel Proust</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>28000</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Chartres</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Carrefour, Av. Marcel Proust, 28000 Chartres, France</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 37 34 04 58</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:00</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:00</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:00</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:00</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:00</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>08:00–19:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="n">
+        <v>0.8411764705882352</v>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Mailliart</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>8 Place De La République</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>72600</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Mamers</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>8 Pl. de la République, 72600 Mamers, France</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 43 97 60 92</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–18:00</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="n">
+        <v>0.8938461538461538</v>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Des Brigadières</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>10 Allée Georges Bizet</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>95870</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Bezons</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>10 All. Georges Bizet, 95870 Bezons, France</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 30 76 94 40</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–20:00</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–20:00</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–20:00</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–20:00</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–20:00</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>09:30–13:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="n">
+        <v>0.8935483870967742</v>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De L'esplanade</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>16 Avenue de la Grande Borne</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>91350</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Viry Châtillon</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>16 Av. de la Grande Borne, 91170 Viry-Châtillon, France</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 69 45 43 44</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="n">
+        <v>0.7799999999999999</v>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Du Lion</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>16 Rue De La Republique</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>57320</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>BOUZONVILLE</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>16 Rue de la République, 57320 Bouzonville, France</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 87 78 33 14</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:00</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="n">
+        <v>0.8943661971830985</v>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Salengro</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>55 Rue Roger Salengro</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>62740</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Fouquieres Les Lens</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>55 Rue Roger Salengro, 62740 Fouquières-lès-Lens, France</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 21 67 17 88</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="n">
+        <v>0.868</v>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De La Place</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>24 Place Du 8 Mai 1945</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>38800</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>LE PONT DE CLAIX</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>24 Pl. du 8 Mai 1945, 38800 Le Pont-de-Claix, France</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 76 98 01 51</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:30
+14:00–18:00</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="n">
+        <v>0.8605633802816901</v>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Du Moulin</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Chemin du pin bernard quartier les plantiers</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>83690</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Salernes</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Chemin du pin bernard quartier les plantiers, 83690 Salernes, France</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 94 67 54 56</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Des Diablots</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>20 Place De Culcheth</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>95320</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>St Leu La Foret</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Centre commercial des Diablots, 20 Pl. de Culcheth, 95320 Saint-Leu-la-Forêt, France</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 30 40 07 54</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>0.702</v>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Breviere</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>56 Avenue de la République</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>16260</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Chasseneuil</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>56 Av. de la République, 16260 Chasseneuil-sur-Bonnieure, France</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>+33 5 45 39 55 40</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="n">
+        <v>0.8517241379310344</v>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Loeuillet</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>58 Rue Du Général Jean Crépin</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>80370</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Bernaville</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>58 Rue du Général Jean Crépin, 80370 Bernaville, France</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 22 32 77 26</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>0.9121951219512194</v>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Des Ormeaux</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2 Rue Des Ormeaux</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>53500</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Montenay</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>2 Rue des Ormeaux, 53500 Montenay, France</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 43 05 11 54</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>0.8821428571428571</v>
+      </c>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Gosselin</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>87 AV BECQUART</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>59130</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>LAMBERSART</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>79 Av. Pottier, 59130 Lambersart, France</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 20 51 50 18</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>0.8176470588235294</v>
+      </c>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Voltaire Roubaix</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>112 Rue Voltaire</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>59100</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Roubaix</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>112 Rue Voltaire, 59100 Roubaix, France</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 20 09 31 78</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="n">
+        <v>0.7902229845626072</v>
+      </c>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Des Bois Rochefort</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>10 14 Avenue Des Freres Lumiere</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>95240</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Cormeilles En Parisis</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>12-14 Av. des Frères Lumière, 95240 Cormeilles-en-Parisis, France</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 30 10 40 54</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>09:00–20:00</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>0.6659875495189587</v>
+      </c>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De Caumont</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Chem. de la Durance,</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>84510</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>CAUMONT SUR DURANCE</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Chem. de la Durance, 84510 Caumont-sur-Durance, France</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 90 23 07 18</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>0.8565217391304347</v>
+      </c>
+    </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Du Bourg</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>367 Rue Du Bourg</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>45770</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Saran</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>367 Rue du Bourg, 45770 Saran, France</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 38 73 23 40</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+15:00–19:00</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+15:00–19:00</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+15:00–19:00</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+15:00–19:00</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+15:00–19:00</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+15:00–19:00</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>0.8168067226890756</v>
+      </c>
+    </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Clemenceau</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>10 Avenue Georges Clemenceau</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>83250</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>La Londe Les Maurese</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>10 Av. Georges Clemenceau, 83250 La Londe-les-Maures, France</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 94 66 81 43</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>08:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>08:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>08:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>08:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>08:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>08:00–12:30
+15:00–19:00</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>0.6949436795994993</v>
+      </c>
+    </row>
+    <row r="77" ht="40" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Lalanne</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Mail De L Ile De France</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>91090</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Lisses</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Mail de l’île de France Centre commercial du long rayage, 91090 Lisses, France</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 60 86 12 70</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>0.8393939393939394</v>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De Bellevigne En Layon</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>2 Rue Victor Hugo</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>49380</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Bellevigne en Layon</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>2 Rue Victor Hugo, 49380 Bellevigne-en-Layon, France</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 41 54 14 02</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>0.8522388059701492</v>
+      </c>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Centrale</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>27 Avenue De La Republique</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>70200</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>LURE</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>27 Av. de la République, 70200 Lure, France</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 84 30 16 64</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–18:00</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>0.8615384615384615</v>
+      </c>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De Glageon</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>18 Rue Roland Rouleau</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>59132</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Glageon</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>18 Rue Roland Rouleau, 59132 Glageon, France</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 27 57 03 71</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>08:45–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Hay</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>54 Place Du General Leclerc</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>45170</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Neuville Aux Bois</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>54 Pl. Général Leclerc, 45170 Neuville-aux-Bois, France</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 38 75 53 66</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="n">
+        <v>0.8594936708860759</v>
+      </c>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Kok</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>3 Rue Des Lombards 27000 Evreux</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>27000</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Evreux</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>3 Rue des Lombards, 27000 Évreux, France</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 32 33 01 05</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>0.9695652173913043</v>
+      </c>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Adami</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>4 Chemin De La Pourranque</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>13170</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>LES PENNES MIRABEAU</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>non trouvé</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Des Flamands</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>9 Rue Du 8 Mai 1945</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>50110</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Cherbourg-En-Cotentin</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>9 Rue du Huit Mai 1945, 50110 Cherbourg-en-Cotentin, France</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 33 22 27 83</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Remy</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>1 Rue Des Promenades</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>54470</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>THIAUCOURT REGNIEVILLE</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>8 Rue des Promenades, 54470 Thiaucourt-Regniéville, France</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 83 80 90 27</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:15
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="86" ht="40" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Des Residences Luxembourg</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>27 Rue De Luxembourg</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>BELFORT</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>27 Rue de Luxembourg, 90000 Belfort, France</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 84 22 72 55</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>0.8967213114754098</v>
+      </c>
+    </row>
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De La Mairie</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>40 Rue Edouard Herriot</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>62118</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Biache St Vaast</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>40 Rue Edouard Herriot, 62118 Biache-Saint-Vaast, France</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 21 50 17 72</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>0.6810916179337232</v>
+      </c>
+    </row>
+    <row r="88" ht="40" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Brunet - Parmentier</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>84 Avenue François Miterrand</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>18000</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Bourges</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>non trouvé</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" ht="40" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Bertrand</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>2 Rue De Lorraine</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>88150</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>THAON LES VOSGES</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>2 Rue de Lorraine, 88150 Thaon-les-Vosges, France</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 29 39 33 24</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:00</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:00</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:00</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:00</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>08:00–20:00</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>08:00–19:00</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>0.7779796511627907</v>
+      </c>
+    </row>
+    <row r="90" ht="40" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Fugeray Page</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>4 Rue De La Republique</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>77460</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Souppes Sur Loing</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>52 Av. du Maréchal Leclerc, 77460 Souppes-sur-Loing, France</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 64 29 70 26</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:00
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>0.7615384615384615</v>
+      </c>
+    </row>
+    <row r="91" ht="40" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Des Ecoles</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>96 Avenue Du Canigou</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>66170</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>St Feliu D Avall</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>96 Av. du Canigou, 66170 Saint-Féliu-d'Avall, France</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 68 57 80 19</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:00</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+    </row>
+    <row r="92" ht="40" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Du Pôle Médical</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>4 rue du Docteur René Marques</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>66250</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Saint Laurent de la Salanque</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>4 Rue du Dr René Marquès, 66250 Saint-Laurent-de-la-Salanque, France</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 68 28 30 58</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="n">
+        <v>0.851578947368421</v>
+      </c>
+    </row>
+    <row r="93" ht="40" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De La Traverse Pole Sante</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Rue Raymond Souday</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>76410</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Cleon</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>52 Rue Raymond Souday, 76410 Cléon, France</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 35 81 76 06</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>0.7612068965517241</v>
+      </c>
+    </row>
+    <row r="94" ht="40" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De La Douve</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>13 Rue De La Marne</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>50360</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Picauville</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>13 Rue de la Marne, 50360 Picauville, France</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>+33 2 33 41 04 92</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+13:30–19:00</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="n">
+        <v>0.8799999999999999</v>
+      </c>
+    </row>
+    <row r="95" ht="40" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De L Arche -Lemonnier</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>14 Rue Jean Prieur</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>27340</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Pont De L Arche</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>non trouvé</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" ht="40" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie La Marinade</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>10B Avenue De La Cote Vermeille</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>66250</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>ST LAURENT DE LA SALANQUE</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>10 Bis Av. de la Côté Vermeille, 66250 Saint-Laurent-de-la-Salanque, France</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 68 28 63 63</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:30–19:30</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="n">
+        <v>0.6461704422869471</v>
+      </c>
+    </row>
+    <row r="97" ht="40" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Ogeuloise - Barreyat</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>112 Avenue D'Ossau</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>64680</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>OGEU LES BAINS</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>112 Av. Dossau, 64680 Ogeu-les-Bains, France</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>+33 5 59 34 92 65</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P97" s="3" t="n">
+        <v>0.7364587089794445</v>
+      </c>
+    </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Milliane</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>68 Boulevard Alsace Lorraine</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>9100</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Pamiers</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>68 Bd Alsace Lorraine, 09100 Pamiers, France</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>+33 5 61 67 01 82</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>08:30–19:30</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>08:30–18:30</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>0.8415384615384616</v>
+      </c>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Du Breucq</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>140 Rue Jean Jaures</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>59491</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Villeneuve D'Ascq</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>140 Rue Jean Jaurès, 59491 Villeneuve-d'Ascq, France</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>+33 3 20 72 28 02</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>09:00–13:00
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="n">
+        <v>0.8652173913043477</v>
+      </c>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Centrale Des Pyrenees</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>127 Rue Des Pyrenees</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>75020</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>PARIS</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>non trouvé</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+      <c r="P100" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie Des Allees</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>10 Allee De La Republique</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>33350</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Castillon La Bataille</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>10 All. de la République, 33350 Castillon-la-Bataille, France</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>+33 5 57 40 01 44</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:30</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="n">
+        <v>0.8662650602409638</v>
+      </c>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Pharmacie De Lagnes</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Rue De La Republique</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>84800</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>LAGNES</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>trouvé</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>235 Route du Stade, 84800 Lagnes, France</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>+33 4 90 20 30 85</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>08:30–12:30
+14:00–19:00</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>09:00–12:30</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Fermé</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="n">
+        <v>0.6826284970722185</v>
       </c>
     </row>
   </sheetData>
